--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-digital-certificate.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-digital-certificate</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -467,32 +467,19 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>Extension.extension:validity.value[x]:valuePeriod</t>
-  </si>
-  <si>
-    <t>valuePeriod</t>
-  </si>
-  <si>
-    <t>Extension.extension:validity.value[x]:valuePeriod.id</t>
+    <t>Extension.extension:validity.value[x].id</t>
   </si>
   <si>
     <t>Extension.extension.value[x].id</t>
   </si>
   <si>
-    <t>Extension.extension:validity.value[x]:valuePeriod.extension</t>
+    <t>Extension.extension:validity.value[x].extension</t>
   </si>
   <si>
     <t>Extension.extension.value[x].extension</t>
   </si>
   <si>
-    <t>Extension.extension:validity.value[x]:valuePeriod.start</t>
+    <t>Extension.extension:validity.value[x].start</t>
   </si>
   <si>
     <t>Extension.extension.value[x].start</t>
@@ -524,7 +511,7 @@
     <t>./low</t>
   </si>
   <si>
-    <t>Extension.extension:validity.value[x]:valuePeriod.end</t>
+    <t>Extension.extension:validity.value[x].end</t>
   </si>
   <si>
     <t>Extension.extension.value[x].end</t>
@@ -938,10 +925,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK46"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="55.984375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.578125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="13.38671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
@@ -3457,14 +3444,16 @@
         <v>75</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="AC24" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>119</v>
@@ -3487,14 +3476,12 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="C25" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>147</v>
+      </c>
+      <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>75</v>
       </c>
@@ -3515,13 +3502,13 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3572,7 +3559,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -3581,32 +3568,32 @@
         <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
@@ -3618,15 +3605,17 @@
         <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>92</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>75</v>
@@ -3663,53 +3652,53 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -3718,19 +3707,19 @@
         <v>75</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>89</v>
+        <v>153</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>90</v>
+        <v>154</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>91</v>
+        <v>155</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>92</v>
+        <v>156</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3768,42 +3757,42 @@
         <v>75</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>96</v>
+        <v>157</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3823,25 +3812,27 @@
         <v>75</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q28" s="2"/>
+      <c r="Q28" t="s" s="2">
+        <v>165</v>
+      </c>
       <c r="R28" t="s" s="2">
         <v>75</v>
       </c>
@@ -3885,7 +3876,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -3894,23 +3885,25 @@
         <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>120</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>75</v>
       </c>
@@ -3928,27 +3921,25 @@
         <v>75</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>156</v>
+        <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>157</v>
+        <v>89</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q29" t="s" s="2">
-        <v>169</v>
-      </c>
+      <c r="Q29" s="2"/>
       <c r="R29" t="s" s="2">
         <v>75</v>
       </c>
@@ -3992,22 +3983,22 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>170</v>
+        <v>96</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>162</v>
+        <v>79</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>171</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30">
@@ -4015,11 +4006,9 @@
         <v>172</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="C30" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>75</v>
       </c>
@@ -4040,17 +4029,15 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>174</v>
+        <v>83</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -4099,30 +4086,30 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4133,7 +4120,7 @@
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>75</v>
@@ -4145,13 +4132,13 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4190,42 +4177,42 @@
         <v>75</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4233,10 +4220,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>75</v>
@@ -4248,22 +4235,24 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>75</v>
@@ -4293,42 +4282,42 @@
         <v>75</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4336,7 +4325,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>81</v>
@@ -4351,24 +4340,22 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>75</v>
@@ -4410,19 +4397,19 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>98</v>
@@ -4430,12 +4417,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>75</v>
       </c>
@@ -4456,15 +4445,17 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>117</v>
+        <v>178</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -4513,22 +4504,22 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="35">
@@ -4536,11 +4527,9 @@
         <v>180</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="C35" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>75</v>
       </c>
@@ -4561,17 +4550,15 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>182</v>
+        <v>83</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>183</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>75</v>
@@ -4620,30 +4607,30 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4654,7 +4641,7 @@
         <v>76</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>75</v>
@@ -4666,13 +4653,13 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4711,42 +4698,42 @@
         <v>75</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4754,10 +4741,10 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>75</v>
@@ -4769,22 +4756,24 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>75</v>
+        <v>177</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>75</v>
@@ -4814,42 +4803,42 @@
         <v>75</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4857,7 +4846,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>81</v>
@@ -4872,24 +4861,22 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" t="s" s="2">
-        <v>181</v>
+        <v>75</v>
       </c>
       <c r="S38" t="s" s="2">
         <v>75</v>
@@ -4931,19 +4918,19 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>98</v>
@@ -4951,12 +4938,14 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
@@ -4977,15 +4966,17 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>117</v>
+        <v>186</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5034,22 +5025,22 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
     </row>
     <row r="40">
@@ -5057,11 +5048,9 @@
         <v>188</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>189</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>75</v>
       </c>
@@ -5082,17 +5071,15 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>191</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -5141,30 +5128,30 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5175,7 +5162,7 @@
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
@@ -5187,13 +5174,13 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5232,42 +5219,42 @@
         <v>75</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5275,10 +5262,10 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -5290,22 +5277,24 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>28</v>
+        <v>111</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="S42" t="s" s="2">
         <v>75</v>
@@ -5335,42 +5324,42 @@
         <v>75</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5378,7 +5367,7 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>81</v>
@@ -5393,24 +5382,22 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>75</v>
@@ -5452,19 +5439,19 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>98</v>
@@ -5472,10 +5459,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5483,7 +5470,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>81</v>
@@ -5498,22 +5485,24 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q44" s="2"/>
       <c r="R44" t="s" s="2">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="S44" t="s" s="2">
         <v>75</v>
@@ -5555,19 +5544,19 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>98</v>
@@ -5575,10 +5564,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5586,10 +5575,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
@@ -5601,24 +5590,22 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>110</v>
+        <v>193</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>75</v>
@@ -5660,124 +5647,21 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
-      <c r="P46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AK46" t="s" s="2">
         <v>98</v>
       </c>
     </row>
